--- a/filer/30830415_vkr.xlsx
+++ b/filer/30830415_vkr.xlsx
@@ -6714,7 +6714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6856,22 +6856,28 @@
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>fsa:ProfitLossAfterAttributableToMinorityInterest</t>
+          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
         </is>
       </c>
       <c r="C5" s="34" t="inlineStr">
         <is>
-          <t>fsa:ProfitLossAfterAttributableToMinorityInterest</t>
-        </is>
-      </c>
-      <c r="D5" s="35" t="n"/>
-      <c r="E5" s="35" t="n"/>
-      <c r="F5" s="35" t="n"/>
+          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
+        </is>
+      </c>
+      <c r="D5" s="35" t="n">
+        <v>-108000</v>
+      </c>
+      <c r="E5" s="35" t="n">
+        <v>-14000</v>
+      </c>
+      <c r="F5" s="35" t="n">
+        <v>96000</v>
+      </c>
       <c r="G5" s="35" t="n">
-        <v>4346000</v>
+        <v>205000</v>
       </c>
       <c r="H5" s="35" t="n">
-        <v>3674000</v>
+        <v>8000</v>
       </c>
       <c r="I5" s="36" t="inlineStr">
         <is>
@@ -6887,21 +6893,29 @@
       </c>
       <c r="B6" s="37" t="inlineStr">
         <is>
-          <t>fsa:ProfitLossFromOrdinaryActivitiesAfterTax</t>
+          <t>fsa:ShorttermPayablesToParticipatingInterest</t>
         </is>
       </c>
       <c r="C6" s="37" t="inlineStr">
         <is>
-          <t>fsa:ProfitLossFromOrdinaryActivitiesAfterTax</t>
-        </is>
-      </c>
-      <c r="D6" s="38" t="n"/>
+          <t>fsa:ShorttermPayablesToParticipatingInterest</t>
+        </is>
+      </c>
+      <c r="D6" s="38" t="n">
+        <v>20000</v>
+      </c>
       <c r="E6" s="38" t="n">
-        <v>1573000</v>
-      </c>
-      <c r="F6" s="38" t="n"/>
-      <c r="G6" s="38" t="n"/>
-      <c r="H6" s="38" t="n"/>
+        <v>9000</v>
+      </c>
+      <c r="F6" s="38" t="n">
+        <v>11000</v>
+      </c>
+      <c r="G6" s="38" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H6" s="38" t="n">
+        <v>6000</v>
+      </c>
       <c r="I6" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -6916,104 +6930,30 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
+          <t>fsa:WorkPerformedByEntityAndCapitalised</t>
         </is>
       </c>
       <c r="C7" s="34" t="inlineStr">
         <is>
-          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
+          <t>fsa:WorkPerformedByEntityAndCapitalised</t>
         </is>
       </c>
       <c r="D7" s="35" t="n">
-        <v>-108000</v>
+        <v>-27000</v>
       </c>
       <c r="E7" s="35" t="n">
-        <v>-14000</v>
+        <v>-59000</v>
       </c>
       <c r="F7" s="35" t="n">
-        <v>96000</v>
+        <v>-119000</v>
       </c>
       <c r="G7" s="35" t="n">
-        <v>205000</v>
+        <v>-172000</v>
       </c>
       <c r="H7" s="35" t="n">
-        <v>8000</v>
+        <v>-242000</v>
       </c>
       <c r="I7" s="36" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="37" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B8" s="37" t="inlineStr">
-        <is>
-          <t>fsa:ShorttermPayablesToParticipatingInterest</t>
-        </is>
-      </c>
-      <c r="C8" s="37" t="inlineStr">
-        <is>
-          <t>fsa:ShorttermPayablesToParticipatingInterest</t>
-        </is>
-      </c>
-      <c r="D8" s="38" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E8" s="38" t="n">
-        <v>9000</v>
-      </c>
-      <c r="F8" s="38" t="n">
-        <v>11000</v>
-      </c>
-      <c r="G8" s="38" t="n">
-        <v>8000</v>
-      </c>
-      <c r="H8" s="38" t="n">
-        <v>6000</v>
-      </c>
-      <c r="I8" s="39" t="inlineStr">
-        <is>
-          <t>Ingen forklaring tilgængelig.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="34" t="inlineStr">
-        <is>
-          <t>Øvrige (ukendt)</t>
-        </is>
-      </c>
-      <c r="B9" s="34" t="inlineStr">
-        <is>
-          <t>fsa:WorkPerformedByEntityAndCapitalised</t>
-        </is>
-      </c>
-      <c r="C9" s="34" t="inlineStr">
-        <is>
-          <t>fsa:WorkPerformedByEntityAndCapitalised</t>
-        </is>
-      </c>
-      <c r="D9" s="35" t="n">
-        <v>-27000</v>
-      </c>
-      <c r="E9" s="35" t="n">
-        <v>-59000</v>
-      </c>
-      <c r="F9" s="35" t="n">
-        <v>-119000</v>
-      </c>
-      <c r="G9" s="35" t="n">
-        <v>-172000</v>
-      </c>
-      <c r="H9" s="35" t="n">
-        <v>-242000</v>
-      </c>
-      <c r="I9" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>

--- a/filer/30830415_vkr.xlsx
+++ b/filer/30830415_vkr.xlsx
@@ -648,7 +648,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/30830415_vkr.xlsx
+++ b/filer/30830415_vkr.xlsx
@@ -10,8 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik_30830415" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw_30830415" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw_30830415" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pengestrom_raw_30830415" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -204,9 +205,9 @@
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -628,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L85"/>
+  <dimension ref="A1:L92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -4146,6 +4147,148 @@
       </c>
       <c r="F85" s="13">
         <f>IFERROR($F$26/($F$51+$F$54)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="15" t="inlineStr">
+        <is>
+          <t>PENGESTRØMSOPGØRELSE t.kr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B88" s="17">
+        <f>'pengestrom_raw_30830415'!$B$2</f>
+        <v/>
+      </c>
+      <c r="C88" s="17">
+        <f>'pengestrom_raw_30830415'!$C$2</f>
+        <v/>
+      </c>
+      <c r="D88" s="17">
+        <f>'pengestrom_raw_30830415'!$D$2</f>
+        <v/>
+      </c>
+      <c r="E88" s="17">
+        <f>'pengestrom_raw_30830415'!$E$2</f>
+        <v/>
+      </c>
+      <c r="F88" s="17">
+        <f>'pengestrom_raw_30830415'!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B89" s="17">
+        <f>'pengestrom_raw_30830415'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C89" s="17">
+        <f>'pengestrom_raw_30830415'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D89" s="17">
+        <f>'pengestrom_raw_30830415'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E89" s="17">
+        <f>'pengestrom_raw_30830415'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F89" s="17">
+        <f>'pengestrom_raw_30830415'!$F$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B90" s="17">
+        <f>'pengestrom_raw_30830415'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C90" s="17">
+        <f>'pengestrom_raw_30830415'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D90" s="17">
+        <f>'pengestrom_raw_30830415'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E90" s="17">
+        <f>'pengestrom_raw_30830415'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F90" s="17">
+        <f>'pengestrom_raw_30830415'!$F$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm (rapporteret)</t>
+        </is>
+      </c>
+      <c r="B91" s="17">
+        <f>'pengestrom_raw_30830415'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C91" s="17">
+        <f>'pengestrom_raw_30830415'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D91" s="17">
+        <f>'pengestrom_raw_30830415'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E91" s="17">
+        <f>'pengestrom_raw_30830415'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F91" s="17">
+        <f>'pengestrom_raw_30830415'!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="16" t="inlineStr">
+        <is>
+          <t>Krydstjek: drift + inv. + fin. = årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B92">
+        <f>IF(ABS(('pengestrom_raw_30830415'!$B$2+'pengestrom_raw_30830415'!$B$3+'pengestrom_raw_30830415'!$B$4)-'pengestrom_raw_30830415'!$B$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_30830415'!$B$2+'pengestrom_raw_30830415'!$B$3+'pengestrom_raw_30830415'!$B$4)-'pengestrom_raw_30830415'!$B$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="C92">
+        <f>IF(ABS(('pengestrom_raw_30830415'!$C$2+'pengestrom_raw_30830415'!$C$3+'pengestrom_raw_30830415'!$C$4)-'pengestrom_raw_30830415'!$C$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_30830415'!$C$2+'pengestrom_raw_30830415'!$C$3+'pengestrom_raw_30830415'!$C$4)-'pengestrom_raw_30830415'!$C$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="D92">
+        <f>IF(ABS(('pengestrom_raw_30830415'!$D$2+'pengestrom_raw_30830415'!$D$3+'pengestrom_raw_30830415'!$D$4)-'pengestrom_raw_30830415'!$D$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_30830415'!$D$2+'pengestrom_raw_30830415'!$D$3+'pengestrom_raw_30830415'!$D$4)-'pengestrom_raw_30830415'!$D$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E92">
+        <f>IF(ABS(('pengestrom_raw_30830415'!$E$2+'pengestrom_raw_30830415'!$E$3+'pengestrom_raw_30830415'!$E$4)-'pengestrom_raw_30830415'!$E$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_30830415'!$E$2+'pengestrom_raw_30830415'!$E$3+'pengestrom_raw_30830415'!$E$4)-'pengestrom_raw_30830415'!$E$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="F92">
+        <f>IF(ABS(('pengestrom_raw_30830415'!$F$2+'pengestrom_raw_30830415'!$F$3+'pengestrom_raw_30830415'!$F$4)-'pengestrom_raw_30830415'!$F$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_30830415'!$F$2+'pengestrom_raw_30830415'!$F$3+'pengestrom_raw_30830415'!$F$4)-'pengestrom_raw_30830415'!$F$5,"+#,##0;-#,##0"))</f>
         <v/>
       </c>
     </row>
@@ -4194,379 +4337,379 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Nettoomsætning</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>26093000</v>
       </c>
-      <c r="C2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>31889000</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>29543000</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>28835000</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="F2" s="17" t="n">
         <v>30679000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>113000</v>
       </c>
-      <c r="C3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>830000</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>91000</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>184000</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="F3" s="17" t="n">
         <v>90000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Vareforbrug</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>-658000</v>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>-694000</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>117000</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>425000</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="F4" s="17" t="n">
         <v>-53000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Andre eksterne omkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>6533000</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>7990000</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>7371000</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>7480000</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="17" t="n">
         <v>7581000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="16" t="n"/>
-      <c r="F6" s="16" t="n"/>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Personaleomkostninger</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>6641000</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>8022000</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>7648000</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>7933000</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="17" t="n">
         <v>9156000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Resultat før afskrivninger</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Af- og nedskrivninger</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>936000</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>1121000</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>1061000</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>1099000</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="17" t="n">
         <v>1326000</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>3907000</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>4130000</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>4002000</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>3777000</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <v>3579000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>686000</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>803000</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>760000</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>712000</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>970000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Finansielle indtægter</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>3030000</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>1320000</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>1856000</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>2300000</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="17" t="n">
         <v>2435000</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>620000</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>3471000</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>446000</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>448000</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="17" t="n">
         <v>1308000</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>2410000</v>
       </c>
-      <c r="C15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>-2151000</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>1410000</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>1852000</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="F15" s="17" t="n">
         <v>1126000</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>6371000</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>1994000</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>5421000</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>5634000</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="17" t="n">
         <v>4711000</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>1374000</v>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>421000</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>1246000</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>1288000</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="F17" s="17" t="n">
         <v>1038000</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>4997000</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>1573000</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>4174000</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>4347000</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="17" t="n">
         <v>3673000</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Gns. antal medarbejdere</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>17104</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>20007</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>18181</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>17113</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="F19" s="17" t="n">
         <v>17458</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
+      <c r="B20" s="17" t="n">
         <v>627000</v>
       </c>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4613,870 +4756,870 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Immaterielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>3120000</v>
       </c>
-      <c r="C2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>2769000</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>2510000</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>2241000</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="F2" s="17" t="n">
         <v>3545000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>5383000</v>
       </c>
-      <c r="C3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>5582000</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>6391000</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>7299000</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="F3" s="17" t="n">
         <v>8174000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Finansielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>3968000</v>
       </c>
-      <c r="C4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>4416000</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>5016000</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>6174000</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="F4" s="17" t="n">
         <v>6478000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Anlægsaktiver</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>12471000</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>12768000</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>13918000</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>15715000</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="F5" s="17" t="n">
         <v>18196000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Råvarer og hjælpematerialer</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="16" t="n"/>
-      <c r="F6" s="16" t="n"/>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Varer under fremstilling</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>237000</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>266000</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>253000</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>265000</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="17" t="n">
         <v>655000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Færdigvarer og handelsvarer</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="16" t="n"/>
-      <c r="E8" s="16" t="n"/>
-      <c r="F8" s="16" t="n"/>
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Varebeholdninger</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>3951000</v>
       </c>
-      <c r="C9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>4941000</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>4344000</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>3877000</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="17" t="n">
         <v>4073000</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>2522000</v>
       </c>
-      <c r="C10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>2631000</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>2127000</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>2201000</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="17" t="n">
         <v>2466000</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>7609000</v>
       </c>
-      <c r="C11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>7577000</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>7490000</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>5822000</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="F11" s="17" t="n">
         <v>7419000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Andre tilgodehavender</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>484000</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>844000</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>766000</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>823000</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>810000</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>229000</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>221000</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>253000</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>294000</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="17" t="n">
         <v>309000</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Udskudt skatteaktiv</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>288000</v>
       </c>
-      <c r="C14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>374000</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>307000</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>359000</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="17" t="n">
         <v>358000</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="16" t="n"/>
-      <c r="D15" s="16" t="n"/>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n"/>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>275000</v>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>260000</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>135000</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>238000</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="F16" s="17" t="n">
         <v>103000</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Tilgodehavender</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>4035000</v>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>4596000</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>3841000</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>4180000</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="F17" s="17" t="n">
         <v>4700000</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Værdipapirer</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>13755000</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>11033000</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>13397000</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>14769000</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="F18" s="17" t="n">
         <v>14679000</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Likvide beholdninger</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>823000</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>890000</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>1067000</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>1012000</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="F19" s="17" t="n">
         <v>1142000</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>Omsætningsaktiver</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
+      <c r="B20" s="17" t="n">
         <v>22565000</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="17" t="n">
         <v>21459000</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="17" t="n">
         <v>22650000</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="17" t="n">
         <v>23837000</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="F20" s="17" t="n">
         <v>24594000</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>Aktiver</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n">
+      <c r="B21" s="17" t="n">
         <v>35036000</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="17" t="n">
         <v>34227000</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="17" t="n">
         <v>36568000</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="17" t="n">
         <v>39552000</v>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="F21" s="17" t="n">
         <v>42790000</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Selskabskapital</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n">
+      <c r="B22" s="17" t="n">
         <v>110000</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="17" t="n">
         <v>110000</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="17" t="n">
         <v>110000</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="17" t="n">
         <v>110000</v>
       </c>
-      <c r="F22" s="16" t="n">
+      <c r="F22" s="17" t="n">
         <v>110000</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n"/>
-      <c r="C23" s="16" t="n"/>
-      <c r="D23" s="16" t="n">
+      <c r="B23" s="17" t="n"/>
+      <c r="C23" s="17" t="n"/>
+      <c r="D23" s="17" t="n">
         <v>327000</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="E23" s="17" t="n">
         <v>1137000</v>
       </c>
-      <c r="F23" s="16" t="n">
+      <c r="F23" s="17" t="n">
         <v>1862000</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n"/>
-      <c r="C24" s="16" t="n"/>
-      <c r="D24" s="16" t="n"/>
-      <c r="E24" s="16" t="n"/>
-      <c r="F24" s="16" t="n"/>
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="17" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n">
+      <c r="B25" s="17" t="n">
         <v>-2000</v>
       </c>
-      <c r="C25" s="16" t="n">
+      <c r="C25" s="17" t="n">
         <v>-30000</v>
       </c>
-      <c r="D25" s="16" t="n"/>
-      <c r="E25" s="16" t="n"/>
-      <c r="F25" s="16" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="17" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Andre reserver</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="16" t="n"/>
-      <c r="D26" s="16" t="n"/>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="16" t="n"/>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="17" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>Overført resultat</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n">
+      <c r="B27" s="17" t="n">
         <v>24318000</v>
       </c>
-      <c r="C27" s="16" t="n">
+      <c r="C27" s="17" t="n">
         <v>24925000</v>
       </c>
-      <c r="D27" s="16" t="n">
+      <c r="D27" s="17" t="n">
         <v>28071000</v>
       </c>
-      <c r="E27" s="16" t="n">
+      <c r="E27" s="17" t="n">
         <v>31337000</v>
       </c>
-      <c r="F27" s="16" t="n">
+      <c r="F27" s="17" t="n">
         <v>33847000</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>Egenkapital i alt</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n">
+      <c r="B28" s="17" t="n">
         <v>25320000</v>
       </c>
-      <c r="C28" s="16" t="n">
+      <c r="C28" s="17" t="n">
         <v>26022000</v>
       </c>
-      <c r="D28" s="16" t="n">
+      <c r="D28" s="17" t="n">
         <v>29780000</v>
       </c>
-      <c r="E28" s="16" t="n">
+      <c r="E28" s="17" t="n">
         <v>33157000</v>
       </c>
-      <c r="F28" s="16" t="n">
+      <c r="F28" s="17" t="n">
         <v>35476000</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Hensættelse til udskudt skat</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n">
+      <c r="B29" s="17" t="n">
         <v>509000</v>
       </c>
-      <c r="C29" s="16" t="n">
+      <c r="C29" s="17" t="n">
         <v>380000</v>
       </c>
-      <c r="D29" s="16" t="n">
+      <c r="D29" s="17" t="n">
         <v>416000</v>
       </c>
-      <c r="E29" s="16" t="n">
+      <c r="E29" s="17" t="n">
         <v>454000</v>
       </c>
-      <c r="F29" s="16" t="n">
+      <c r="F29" s="17" t="n">
         <v>564000</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>Hensatte forpligtelser</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n">
+      <c r="B30" s="17" t="n">
         <v>1355000</v>
       </c>
-      <c r="C30" s="16" t="n">
+      <c r="C30" s="17" t="n">
         <v>1361000</v>
       </c>
-      <c r="D30" s="16" t="n">
+      <c r="D30" s="17" t="n">
         <v>1336000</v>
       </c>
-      <c r="E30" s="16" t="n">
+      <c r="E30" s="17" t="n">
         <v>1242000</v>
       </c>
-      <c r="F30" s="16" t="n">
+      <c r="F30" s="17" t="n">
         <v>1560000</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>Langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n">
+      <c r="B31" s="17" t="n">
         <v>1152000</v>
       </c>
-      <c r="C31" s="16" t="n">
+      <c r="C31" s="17" t="n">
         <v>51000</v>
       </c>
-      <c r="D31" s="16" t="n">
+      <c r="D31" s="17" t="n">
         <v>33000</v>
       </c>
-      <c r="E31" s="16" t="n">
+      <c r="E31" s="17" t="n">
         <v>27000</v>
       </c>
-      <c r="F31" s="16" t="n">
+      <c r="F31" s="17" t="n">
         <v>30000</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n"/>
-      <c r="C32" s="16" t="n"/>
-      <c r="D32" s="16" t="n"/>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="16" t="n"/>
+      <c r="B32" s="17" t="n"/>
+      <c r="C32" s="17" t="n"/>
+      <c r="D32" s="17" t="n"/>
+      <c r="E32" s="17" t="n"/>
+      <c r="F32" s="17" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n">
+      <c r="B33" s="17" t="n">
         <v>1153000</v>
       </c>
-      <c r="C33" s="16" t="n">
+      <c r="C33" s="17" t="n">
         <v>1206000</v>
       </c>
-      <c r="D33" s="16" t="n">
+      <c r="D33" s="17" t="n">
         <v>7000</v>
       </c>
-      <c r="E33" s="16" t="n">
+      <c r="E33" s="17" t="n">
         <v>17000</v>
       </c>
-      <c r="F33" s="16" t="n">
+      <c r="F33" s="17" t="n">
         <v>24000</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>Kreditinstitutter</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n">
+      <c r="B34" s="17" t="n">
         <v>268000</v>
       </c>
-      <c r="C34" s="16" t="n">
+      <c r="C34" s="17" t="n">
         <v>1000</v>
       </c>
-      <c r="D34" s="16" t="n">
+      <c r="D34" s="17" t="n">
         <v>1000</v>
       </c>
-      <c r="E34" s="16" t="n">
+      <c r="E34" s="17" t="n">
         <v>2000</v>
       </c>
-      <c r="F34" s="16" t="n">
+      <c r="F34" s="17" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="16" t="n"/>
-      <c r="E35" s="16" t="n"/>
-      <c r="F35" s="16" t="n"/>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="17" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n">
+      <c r="B36" s="17" t="n">
         <v>2065000</v>
       </c>
-      <c r="C36" s="16" t="n">
+      <c r="C36" s="17" t="n">
         <v>2123000</v>
       </c>
-      <c r="D36" s="16" t="n">
+      <c r="D36" s="17" t="n">
         <v>2075000</v>
       </c>
-      <c r="E36" s="16" t="n">
+      <c r="E36" s="17" t="n">
         <v>1750000</v>
       </c>
-      <c r="F36" s="16" t="n">
+      <c r="F36" s="17" t="n">
         <v>1727000</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n">
+      <c r="B37" s="17" t="n">
         <v>1382000</v>
       </c>
-      <c r="C37" s="16" t="n">
+      <c r="C37" s="17" t="n">
         <v>1484000</v>
       </c>
-      <c r="D37" s="16" t="n">
+      <c r="D37" s="17" t="n">
         <v>1677000</v>
       </c>
-      <c r="E37" s="16" t="n">
+      <c r="E37" s="17" t="n">
         <v>1559000</v>
       </c>
-      <c r="F37" s="16" t="n">
+      <c r="F37" s="17" t="n">
         <v>1432000</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
-      <c r="B38" s="16" t="n"/>
-      <c r="C38" s="16" t="n"/>
-      <c r="D38" s="16" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="16" t="n"/>
+      <c r="B38" s="17" t="n"/>
+      <c r="C38" s="17" t="n"/>
+      <c r="D38" s="17" t="n"/>
+      <c r="E38" s="17" t="n"/>
+      <c r="F38" s="17" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Selskabsskat</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n">
+      <c r="B39" s="17" t="n">
         <v>351000</v>
       </c>
-      <c r="C39" s="16" t="n">
+      <c r="C39" s="17" t="n">
         <v>184000</v>
       </c>
-      <c r="D39" s="16" t="n">
+      <c r="D39" s="17" t="n">
         <v>106000</v>
       </c>
-      <c r="E39" s="16" t="n">
+      <c r="E39" s="17" t="n">
         <v>144000</v>
       </c>
-      <c r="F39" s="16" t="n">
+      <c r="F39" s="17" t="n">
         <v>179000</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n"/>
-      <c r="C40" s="16" t="n"/>
-      <c r="D40" s="16" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="16" t="n"/>
+      <c r="B40" s="17" t="n"/>
+      <c r="C40" s="17" t="n"/>
+      <c r="D40" s="17" t="n"/>
+      <c r="E40" s="17" t="n"/>
+      <c r="F40" s="17" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
-      <c r="B41" s="16" t="n">
+      <c r="B41" s="17" t="n">
         <v>3030000</v>
       </c>
-      <c r="C41" s="16" t="n">
+      <c r="C41" s="17" t="n">
         <v>2969000</v>
       </c>
-      <c r="D41" s="16" t="n">
+      <c r="D41" s="17" t="n">
         <v>2955000</v>
       </c>
-      <c r="E41" s="16" t="n">
+      <c r="E41" s="17" t="n">
         <v>2943000</v>
       </c>
-      <c r="F41" s="16" t="n">
+      <c r="F41" s="17" t="n">
         <v>3075000</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n">
+      <c r="B42" s="17" t="n">
         <v>321000</v>
       </c>
-      <c r="C42" s="16" t="n">
+      <c r="C42" s="17" t="n">
         <v>301000</v>
       </c>
-      <c r="D42" s="16" t="n">
+      <c r="D42" s="17" t="n">
         <v>265000</v>
       </c>
-      <c r="E42" s="16" t="n">
+      <c r="E42" s="17" t="n">
         <v>260000</v>
       </c>
-      <c r="F42" s="16" t="n">
+      <c r="F42" s="17" t="n">
         <v>711000</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="17" t="inlineStr">
+      <c r="A43" s="15" t="inlineStr">
         <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B43" s="16" t="n">
+      <c r="B43" s="17" t="n">
         <v>7210000</v>
       </c>
-      <c r="C43" s="16" t="n">
+      <c r="C43" s="17" t="n">
         <v>6793000</v>
       </c>
-      <c r="D43" s="16" t="n">
+      <c r="D43" s="17" t="n">
         <v>5419000</v>
       </c>
-      <c r="E43" s="16" t="n">
+      <c r="E43" s="17" t="n">
         <v>5125000</v>
       </c>
-      <c r="F43" s="16" t="n">
+      <c r="F43" s="17" t="n">
         <v>5723000</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="17" t="inlineStr">
+      <c r="A44" s="15" t="inlineStr">
         <is>
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n">
+      <c r="B44" s="17" t="n">
         <v>8362000</v>
       </c>
-      <c r="C44" s="16" t="n">
+      <c r="C44" s="17" t="n">
         <v>6844000</v>
       </c>
-      <c r="D44" s="16" t="n">
+      <c r="D44" s="17" t="n">
         <v>5452000</v>
       </c>
-      <c r="E44" s="16" t="n">
+      <c r="E44" s="17" t="n">
         <v>5153000</v>
       </c>
-      <c r="F44" s="16" t="n">
+      <c r="F44" s="17" t="n">
         <v>5754000</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="17" t="inlineStr">
+      <c r="A45" s="15" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B45" s="16" t="n">
+      <c r="B45" s="17" t="n">
         <v>35036000</v>
       </c>
-      <c r="C45" s="16" t="n">
+      <c r="C45" s="17" t="n">
         <v>34227000</v>
       </c>
-      <c r="D45" s="16" t="n">
+      <c r="D45" s="17" t="n">
         <v>36568000</v>
       </c>
-      <c r="E45" s="16" t="n">
+      <c r="E45" s="17" t="n">
         <v>39552000</v>
       </c>
-      <c r="F45" s="16" t="n">
+      <c r="F45" s="17" t="n">
         <v>42790000</v>
       </c>
     </row>
@@ -5486,6 +5629,122 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse (t.kr.)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>2597000</v>
+      </c>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="17" t="n"/>
+      <c r="F2" s="17" t="n">
+        <v>4070000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>-4231000</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>-1172000</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>-3043000</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>-2482000</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>-3203000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>1054000</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>-1613000</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>-1988000</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>-1206000</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>-747000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6708,7 +6967,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
